--- a/docs/well-architected-radar.xlsx
+++ b/docs/well-architected-radar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wilsonmar/gmail_acct/wilsonmar.github.io/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA954D23-7ADA-6948-8487-A5D753D71713}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D16ED5-2E6E-214E-854F-281A4BB03BAA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="60" windowWidth="28040" windowHeight="17440" xr2:uid="{8E379CFF-0729-5441-9FF8-A7AE69E37479}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Operational Excellence</t>
   </si>
@@ -42,23 +42,26 @@
     <t>Cost Optimization</t>
   </si>
   <si>
-    <t>Next: 2022-Q1</t>
-  </si>
-  <si>
     <t>Now: 2021-Q4</t>
   </si>
   <si>
-    <t>at ___</t>
+    <t>Delta:</t>
   </si>
   <si>
-    <t>Radar Chart for Well-Architected AWS</t>
+    <t>Next:2022-Q1</t>
+  </si>
+  <si>
+    <t>AWS at ___</t>
+  </si>
+  <si>
+    <t>Radar Chart for Well-Architected</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -75,6 +78,14 @@
     </font>
     <font>
       <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -103,11 +114,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -161,14 +173,14 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" sz="2000"/>
-              <a:t>Radar Chart for Well-Architected AWS at </a:t>
+              <a:t>Radar Chart for Well-Architected</a:t>
             </a:r>
             <a:br>
               <a:rPr lang="en-US" sz="2000"/>
             </a:br>
             <a:r>
               <a:rPr lang="en-US" sz="2000"/>
-              <a:t>___</a:t>
+              <a:t>AWS at ___</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -209,8 +221,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.35622112534440664"/>
-          <c:y val="0.24812533707259191"/>
+          <c:x val="0.37100848530717395"/>
+          <c:y val="0.21166916798585553"/>
           <c:w val="0.33212235998339851"/>
           <c:h val="0.61283399848991482"/>
         </c:manualLayout>
@@ -262,13 +274,13 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>Security</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Reliability</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Operational Excellence</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Security</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Reliability</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Performance Efficiency</c:v>
@@ -286,10 +298,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.4</c:v>
@@ -318,7 +330,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Next: 2022-Q1</c:v>
+                  <c:v>Next:2022-Q1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -353,13 +365,13 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>Security</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Reliability</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Operational Excellence</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Security</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Reliability</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Performance Efficiency</c:v>
@@ -377,13 +389,13 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.5</c:v>
@@ -532,8 +544,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11869562053357011"/>
-          <c:y val="0.21049315068493152"/>
+          <c:x val="4.4758467113976748E-2"/>
+          <c:y val="0.22093706955037931"/>
           <c:w val="0.20858675244152705"/>
           <c:h val="0.12558343220796031"/>
         </c:manualLayout>
@@ -1160,16 +1172,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>546100</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1494,63 +1506,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B03A56-BA96-A740-8081-7D2495C7B5BA}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
-    <col min="2" max="3" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="2" max="3" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D7" si="0">C3-B3</f>
+        <v>0.35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>2</v>
       </c>
       <c r="B5" s="2">
         <v>0.4</v>
       </c>
       <c r="C5" s="2">
-        <v>0.75</v>
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="4">
+        <f>C5-B5</f>
+        <v>9.9999999999999978E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1560,8 +1588,12 @@
       <c r="C6" s="2">
         <v>0.5</v>
       </c>
+      <c r="D6" s="4">
+        <f t="shared" si="0"/>
+        <v>0.14999999999999997</v>
+      </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1571,11 +1603,12 @@
       <c r="C7" s="2">
         <v>0.9</v>
       </c>
+      <c r="D7" s="4">
+        <f t="shared" si="0"/>
+        <v>0.19999999999999996</v>
+      </c>
     </row>
   </sheetData>
-  <sortState ref="B3:B7">
-    <sortCondition ref="B3"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/docs/well-architected-radar.xlsx
+++ b/docs/well-architected-radar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wilsonmar/gmail_acct/wilsonmar.github.io/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D16ED5-2E6E-214E-854F-281A4BB03BAA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E1E26C-00D8-304A-AA9F-05138B775AB0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="60" windowWidth="28040" windowHeight="17440" xr2:uid="{8E379CFF-0729-5441-9FF8-A7AE69E37479}"/>
   </bookViews>
@@ -51,10 +51,10 @@
     <t>Next:2022-Q1</t>
   </si>
   <si>
-    <t>AWS at ___</t>
+    <t>Radar Chart for Well-Architected Pillars</t>
   </si>
   <si>
-    <t>Radar Chart for Well-Architected</t>
+    <t>of {system X} in AWS</t>
   </si>
 </sst>
 </file>
@@ -173,14 +173,14 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" sz="2000"/>
-              <a:t>Radar Chart for Well-Architected</a:t>
+              <a:t>Radar Chart for Well-Architected Pillars</a:t>
             </a:r>
             <a:br>
               <a:rPr lang="en-US" sz="2000"/>
             </a:br>
             <a:r>
               <a:rPr lang="en-US" sz="2000"/>
-              <a:t>AWS at ___</a:t>
+              <a:t>of {system X} in AWS</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1516,12 +1516,12 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>

--- a/docs/well-architected-radar.xlsx
+++ b/docs/well-architected-radar.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wilsonmar/gmail_acct/wilsonmar.github.io/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E1E26C-00D8-304A-AA9F-05138B775AB0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C295B069-50D0-3149-AD60-5646100A781F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="60" windowWidth="28040" windowHeight="17440" xr2:uid="{8E379CFF-0729-5441-9FF8-A7AE69E37479}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" activeTab="1" xr2:uid="{8E379CFF-0729-5441-9FF8-A7AE69E37479}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Calcs" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>Operational Excellence</t>
   </si>
@@ -56,12 +57,42 @@
   <si>
     <t>of {system X} in AWS</t>
   </si>
+  <si>
+    <t>Person A</t>
+  </si>
+  <si>
+    <t>Person B</t>
+  </si>
+  <si>
+    <t>Person C</t>
+  </si>
+  <si>
+    <t>Person D</t>
+  </si>
+  <si>
+    <t>Person E</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Generated:</t>
+  </si>
+  <si>
+    <t>Now</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>Initial opinions of Now:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -92,6 +123,75 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="12"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -114,12 +214,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -235,7 +361,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$2</c:f>
+              <c:f>Sheet1!$C$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -270,7 +396,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$7</c:f>
+              <c:f>Sheet1!$B$3:$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -293,7 +419,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$B$7</c:f>
+              <c:f>Sheet1!$C$3:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
@@ -326,7 +452,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$2</c:f>
+              <c:f>Sheet1!$D$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -361,7 +487,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$7</c:f>
+              <c:f>Sheet1!$B$3:$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -384,7 +510,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$3:$C$7</c:f>
+              <c:f>Sheet1!$D$3:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1172,13 +1298,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>88900</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>355600</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
@@ -1506,104 +1632,120 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B03A56-BA96-A740-8081-7D2495C7B5BA}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.1640625" customWidth="1"/>
-    <col min="2" max="3" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" customWidth="1"/>
+    <col min="3" max="4" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
         <v>0.5</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="2">
         <v>0.85</v>
       </c>
-      <c r="D3" s="4">
-        <f t="shared" ref="D3:D7" si="0">C3-B3</f>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E7" si="0">D3-C3</f>
         <v>0.35</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2">
         <v>0.4</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D4" s="2">
         <v>0.75</v>
       </c>
-      <c r="D4" s="4">
+      <c r="E4" s="3">
         <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="2">
+      <c r="C5" s="2">
         <v>0.4</v>
       </c>
-      <c r="C5" s="2">
+      <c r="D5" s="2">
         <v>0.5</v>
       </c>
-      <c r="D5" s="4">
-        <f>C5-B5</f>
+      <c r="E5" s="3">
+        <f>D5-C5</f>
         <v>9.9999999999999978E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2">
+      <c r="C6" s="2">
         <v>0.35000000000000003</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D6" s="2">
         <v>0.5</v>
       </c>
-      <c r="D6" s="4">
+      <c r="E6" s="3">
         <f t="shared" si="0"/>
         <v>0.14999999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2">
+      <c r="C7" s="2">
         <v>0.70000000000000007</v>
       </c>
-      <c r="C7" s="2">
+      <c r="D7" s="2">
         <v>0.9</v>
       </c>
-      <c r="D7" s="4">
+      <c r="E7" s="3">
         <f t="shared" si="0"/>
         <v>0.19999999999999996</v>
       </c>
@@ -1612,4 +1754,275 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E483759-CB80-A74E-A6DE-EE7A02967881}">
+  <dimension ref="A2:I14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="10"/>
+    <col min="4" max="7" width="10.83203125" style="7"/>
+    <col min="8" max="8" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14">
+        <f>AVERAGE(D3:I3)</f>
+        <v>0.8600000000000001</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E3" s="7">
+        <f>D3+0.1</f>
+        <v>0.9</v>
+      </c>
+      <c r="F3" s="7">
+        <f>D3-0.1</f>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="G3" s="7">
+        <f>D3+0.15</f>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="H3" s="2">
+        <f>D3+0.15</f>
+        <v>0.95000000000000007</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="14">
+        <f>AVERAGE(D4:I4)</f>
+        <v>0.46000000000000008</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" ref="E4:E7" si="0">D4+0.1</f>
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" ref="F4:F7" si="1">D4-0.1</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="G4" s="7">
+        <f t="shared" ref="G4:G7" si="2">D4+0.15</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" ref="H4:H7" si="3">D4+0.15</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14">
+        <f>AVERAGE(D5:I5)</f>
+        <v>0.73000000000000009</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.67</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" si="0"/>
+        <v>0.77</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" si="1"/>
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="2"/>
+        <v>0.82000000000000006</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="3"/>
+        <v>0.82000000000000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="14">
+        <f>AVERAGE(D6:I6)</f>
+        <v>0.41</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="0"/>
+        <v>0.45000000000000007</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="7">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="14">
+        <f>AVERAGE(D7:I7)</f>
+        <v>0.76</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="E7" s="7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" si="1"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="2"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="3"/>
+        <v>0.85000000000000009</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <f>A3</f>
+        <v>1</v>
+      </c>
+      <c r="B10" t="str">
+        <f>B3</f>
+        <v>Security</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <f t="shared" ref="A11:B11" si="4">A4</f>
+        <v>2</v>
+      </c>
+      <c r="B11" t="str">
+        <f t="shared" si="4"/>
+        <v>Reliability</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <f t="shared" ref="A12:B12" si="5">A5</f>
+        <v>3</v>
+      </c>
+      <c r="B12" t="str">
+        <f t="shared" si="5"/>
+        <v>Operational Excellence</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <f t="shared" ref="A13:B13" si="6">A6</f>
+        <v>4</v>
+      </c>
+      <c r="B13" t="str">
+        <f t="shared" si="6"/>
+        <v>Performance Efficiency</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <f t="shared" ref="A14:B14" si="7">A7</f>
+        <v>5</v>
+      </c>
+      <c r="B14" t="str">
+        <f t="shared" si="7"/>
+        <v>Cost Optimization</v>
+      </c>
+      <c r="C14" s="11">
+        <v>0.70000000000000007</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/well-architected-radar.xlsx
+++ b/docs/well-architected-radar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wilsonmar/gmail_acct/wilsonmar.github.io/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C295B069-50D0-3149-AD60-5646100A781F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B30FD2-9DB6-114D-BF1D-EFE473FA082C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" activeTab="1" xr2:uid="{8E379CFF-0729-5441-9FF8-A7AE69E37479}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{8E379CFF-0729-5441-9FF8-A7AE69E37479}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
